--- a/05_Figures/F06_prediction/proteins/total/comp_hypertrophy/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/total/comp_hypertrophy/spls/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="215">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -134,498 +134,501 @@
     <t xml:space="preserve">EIF4A2</t>
   </si>
   <si>
+    <t xml:space="preserve">PPIF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADSS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COX20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECI1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDH1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIMS3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEPTIN9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRSF2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMK2D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FECH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLUL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIP2</t>
+  </si>
+  <si>
     <t xml:space="preserve">GLRX5</t>
   </si>
   <si>
-    <t xml:space="preserve">PPIF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADSS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COX20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECI1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IDH1</t>
+    <t xml:space="preserve">NAXE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSFM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD23B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LMCD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PACSIN3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PBXIP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDLIM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLIN2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TXNRD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PADI2</t>
   </si>
   <si>
     <t xml:space="preserve">PALMD</t>
   </si>
   <si>
-    <t xml:space="preserve">SRSF2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAMK2D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FECH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLUL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIMS3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEPTIN9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLIP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAXE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD23B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSFM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PACSIN3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PBXIP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDLIM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXNRD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LMCD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PADI2</t>
-  </si>
-  <si>
     <t xml:space="preserve">PGAM2</t>
   </si>
   <si>
     <t xml:space="preserve">PM20D2</t>
   </si>
   <si>
+    <t xml:space="preserve">ARMT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COQ3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HINT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSPB8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LYPLA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MGLL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FBLN5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STOML2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIFM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRSF1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PANK4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STXBP3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACY1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLVRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CYB5R1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECI2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FBP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HDHD2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP2K3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NNMT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHKG1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPM1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSAP</t>
+  </si>
+  <si>
     <t xml:space="preserve">TPPP3</t>
   </si>
   <si>
-    <t xml:space="preserve">CLIP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COQ3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HINT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSPB8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STXBP3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LYPLA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MGLL</t>
+    <t xml:space="preserve">AFG3L2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIMP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDH1L1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDH3A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATPAF2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DYNC1LI1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF5B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENO2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENOPH1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPHX1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FTH1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDH2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP2K6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPRE3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MLEC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MLIP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPS18B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFAF5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NT5C3A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUVBL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTNL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STX7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMEM205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACAD10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACO1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACSL3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACYP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKR1C3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDH2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANXA11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARPC4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BDH2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPNT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CFL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHCHD10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHMP1B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLTB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COX7A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSTB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHRS7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DLAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUSP3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DYNC1I2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EEF1D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ETF1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FARSB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GFM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPHN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRHPR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHATL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HINT3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HK1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HLA-DRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HNRNPA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HUWE1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDH3G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ILVBL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISCU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LDB3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP1LC3B2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPRE2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPS17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NPLOC4</t>
   </si>
   <si>
     <t xml:space="preserve">NQO2</t>
   </si>
   <si>
-    <t xml:space="preserve">STOML2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIFM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FBLN5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFAF5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PANK4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLIN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACY1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLVRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CYB5R1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECI2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FBP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRSF1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HDHD2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAP2K3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NNMT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPM1A</t>
+    <t xml:space="preserve">NTPCR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OGDH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDHB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PGM5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PGP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHKA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHKB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PKM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLIN3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP3CB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PREP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSAPL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMD6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTPN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBBP7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL13A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL7A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RRAS2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RSU1</t>
   </si>
   <si>
     <t xml:space="preserve">RTN3</t>
   </si>
   <si>
-    <t xml:space="preserve">AFG3L2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIMP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDH1L1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDH3A2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATPAF2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CALU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DYNC1LI1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF5B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENO2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENOPH1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPHX1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FTH1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IDH2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAP2K6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAPRE3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MLEC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NT5C3A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OXCT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHKG1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTNL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STX7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMEM205</t>
+    <t xml:space="preserve">RYR1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SGCD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC25A20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC25A3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC25A6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNX3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STUB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUCLG1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYNE2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TACC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THOP1</t>
   </si>
   <si>
     <t xml:space="preserve">TMX1</t>
   </si>
   <si>
-    <t xml:space="preserve">ACAD10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACO1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACSL3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACYP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKR1C3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDH2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANXA11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARF5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARMT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARPC4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BDH2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BPNT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CFL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHMP2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLTB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COX7A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSTB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHRS7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DLAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUSP3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EEF1D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ETF1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FARSA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FARSB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GFM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRHPR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HHATL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HINT3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HK1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HLA-DRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HNRNPA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HUWE1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IDH3G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ILVBL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ISCU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IVD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAMTOR1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LDB3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAPRE2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MLIP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPS17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPS18B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NPLOC4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NTPCR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OGDH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDHB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PGM5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PGP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHKA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PKM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLIN3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP1R1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP3CB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PREP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSAPL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMD6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PTPN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RBBP7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL7A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RRAS2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RSU1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RYR1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SGCD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC25A20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC25A3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC25A6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNX3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUCLG1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SYNE2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TACC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THOP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIMM50</t>
-  </si>
-  <si>
     <t xml:space="preserve">TRIM72</t>
   </si>
   <si>
@@ -639,6 +642,9 @@
   </si>
   <si>
     <t xml:space="preserve">TXLNB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBAC1</t>
   </si>
   <si>
     <t xml:space="preserve">UBE2V1</t>
@@ -1040,16 +1046,16 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.41819349605132</v>
+        <v>-1.41779861223299</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.217582417582418</v>
+        <v>-0.235164835164835</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -1073,29 +1079,21 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.41819349605132</v>
+        <v>-1.41779861223299</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.217582417582418</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.800995024875622</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.497512437810945</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.816582134169912</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.745275098774612</v>
-      </c>
+        <v>-0.235164835164835</v>
+      </c>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1119,2206 +1117,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-1.37357684926098</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="n">
-        <v>-3.02318492785624</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-0.174487569196195</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-1.09075478152043</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-1.61818454136457</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-0.260693136475544</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-1.97696130835467</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-1.22062791912454</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-2.18594457053426</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-0.500146360789207</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-2.18695021056899</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.756989857617135</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-0.651345643201712</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-0.697767195782218</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-1.83112563402405</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-1.07048536000909</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.172707467398207</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-0.791884511391022</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-1.65686653490415</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-2.57834822021914</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-0.33593138662406</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-1.11638309567348</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-2.27677062512028</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-1.44361865130704</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-0.441767101638725</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-0.845841699646037</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-1.12567324008362</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0.048145918692699</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="n">
-        <v>-0.375661937588034</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="n">
-        <v>-0.663374055393493</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="n">
-        <v>-0.800416256836656</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="n">
-        <v>-1.48825997023215</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-0.612259993753228</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="n">
-        <v>-0.324556546959339</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-0.90873681948212</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-1.19285435480711</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-0.84822735231186</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-0.25114293899183</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-1.71634764134469</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-1.35711434458211</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-1.56316461428506</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" t="n">
-        <v>-1.99682528772886</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" t="n">
-        <v>0.0563014492399286</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" t="n">
-        <v>-0.068826573031979</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" t="n">
-        <v>-1.15326734270018</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" t="n">
-        <v>-1.25115470333419</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" t="n">
-        <v>-0.874150376547968</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" t="n">
-        <v>-0.728725639039192</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-0.853652491064527</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-0.37703202291957</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-0.350634029228897</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-0.307283079031087</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-0.856650450215517</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-0.508789559983106</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" t="n">
-        <v>-0.991472296792914</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" t="n">
-        <v>-0.356116332775463</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" t="n">
-        <v>-0.213476890969374</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" t="n">
-        <v>-1.41069797001709</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" t="n">
-        <v>-2.03793101276725</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" t="n">
-        <v>-0.638863355406914</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" t="n">
-        <v>-1.10964445809287</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" t="n">
-        <v>-1.58866292340469</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" t="n">
-        <v>-1.05517448847147</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" t="n">
-        <v>-0.85738103581575</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" t="n">
-        <v>-0.487941932563895</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" t="n">
-        <v>-1.38900673126773</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="n">
-        <v>0.245817009676914</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="n">
-        <v>0.149448893283827</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>15</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="n">
-        <v>-1.05820381298431</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="n">
-        <v>-0.184623194659855</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="n">
-        <v>-0.327159270348072</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="n">
-        <v>-0.598806369877719</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="n">
-        <v>-1.83124028691513</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="n">
-        <v>-0.921825730946801</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="n">
-        <v>0.137702219881371</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="n">
-        <v>0.0302619993793944</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="n">
-        <v>0.133366530541519</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="n">
-        <v>-0.967199850750534</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" t="n">
-        <v>-0.301697223939598</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" t="n">
-        <v>-0.963720956290214</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>15</v>
-      </c>
-      <c r="B82" t="s">
-        <v>16</v>
-      </c>
-      <c r="C82" t="n">
-        <v>-0.84104853247774</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" t="n">
-        <v>-0.645658660018986</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>15</v>
-      </c>
-      <c r="B84" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" t="n">
-        <v>-1.78327446135383</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" t="n">
-        <v>-0.680926130081678</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" t="s">
-        <v>16</v>
-      </c>
-      <c r="C86" t="n">
-        <v>-0.469714821981311</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" t="n">
-        <v>-0.332763878491276</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" t="n">
-        <v>-0.0723115219501254</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" t="s">
-        <v>16</v>
-      </c>
-      <c r="C89" t="n">
-        <v>-0.3338597652121</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>15</v>
-      </c>
-      <c r="B90" t="s">
-        <v>16</v>
-      </c>
-      <c r="C90" t="n">
-        <v>-0.628950318415388</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" t="s">
-        <v>16</v>
-      </c>
-      <c r="C91" t="n">
-        <v>-2.64680067058651</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" t="s">
-        <v>16</v>
-      </c>
-      <c r="C92" t="n">
-        <v>-1.7830169872409</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" t="n">
-        <v>-0.678536225016674</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" t="s">
-        <v>16</v>
-      </c>
-      <c r="C94" t="n">
-        <v>-0.380634812992132</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" t="s">
-        <v>16</v>
-      </c>
-      <c r="C95" t="n">
-        <v>-0.884715246225235</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B96" t="s">
-        <v>16</v>
-      </c>
-      <c r="C96" t="n">
-        <v>0.00205573696093309</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>15</v>
-      </c>
-      <c r="B97" t="s">
-        <v>16</v>
-      </c>
-      <c r="C97" t="n">
-        <v>0.259671003586652</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B98" t="s">
-        <v>16</v>
-      </c>
-      <c r="C98" t="n">
-        <v>-1.71080268480679</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B99" t="s">
-        <v>16</v>
-      </c>
-      <c r="C99" t="n">
-        <v>0.401612134311441</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" t="s">
-        <v>16</v>
-      </c>
-      <c r="C100" t="n">
-        <v>0.528482344162794</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" t="s">
-        <v>16</v>
-      </c>
-      <c r="C101" t="n">
-        <v>-0.602173248322587</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" t="s">
-        <v>16</v>
-      </c>
-      <c r="C102" t="n">
-        <v>-0.440338341944906</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" t="s">
-        <v>16</v>
-      </c>
-      <c r="C103" t="n">
-        <v>0.524420706565428</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" t="s">
-        <v>16</v>
-      </c>
-      <c r="C104" t="n">
-        <v>-0.50779151069835</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" t="s">
-        <v>16</v>
-      </c>
-      <c r="C105" t="n">
-        <v>0.511967126614851</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>15</v>
-      </c>
-      <c r="B106" t="s">
-        <v>16</v>
-      </c>
-      <c r="C106" t="n">
-        <v>-0.967187995430612</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" t="s">
-        <v>16</v>
-      </c>
-      <c r="C107" t="n">
-        <v>-1.67036470485384</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>15</v>
-      </c>
-      <c r="B108" t="s">
-        <v>16</v>
-      </c>
-      <c r="C108" t="n">
-        <v>0.133073923577627</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" t="s">
-        <v>16</v>
-      </c>
-      <c r="C109" t="n">
-        <v>0.334623011789681</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" t="s">
-        <v>16</v>
-      </c>
-      <c r="C110" t="n">
-        <v>0.123362787779157</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" t="s">
-        <v>16</v>
-      </c>
-      <c r="C111" t="n">
-        <v>-2.33185879630143</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" t="s">
-        <v>16</v>
-      </c>
-      <c r="C112" t="n">
-        <v>-0.660374868182769</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" t="s">
-        <v>16</v>
-      </c>
-      <c r="C113" t="n">
-        <v>-0.890501708979102</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" t="s">
-        <v>16</v>
-      </c>
-      <c r="C114" t="n">
-        <v>-1.29085476165792</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" t="s">
-        <v>16</v>
-      </c>
-      <c r="C115" t="n">
-        <v>0.152000982378883</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>15</v>
-      </c>
-      <c r="B116" t="s">
-        <v>16</v>
-      </c>
-      <c r="C116" t="n">
-        <v>-0.397591678158288</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117" t="s">
-        <v>16</v>
-      </c>
-      <c r="C117" t="n">
-        <v>0.153429846862078</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" t="s">
-        <v>16</v>
-      </c>
-      <c r="C118" t="n">
-        <v>0.0278773377966295</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" t="s">
-        <v>16</v>
-      </c>
-      <c r="C119" t="n">
-        <v>-0.626951719973364</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" t="s">
-        <v>16</v>
-      </c>
-      <c r="C120" t="n">
-        <v>-0.44197913158967</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" t="s">
-        <v>16</v>
-      </c>
-      <c r="C121" t="n">
-        <v>-0.639863833807901</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" t="s">
-        <v>16</v>
-      </c>
-      <c r="C122" t="n">
-        <v>-2.0092351615188</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" t="s">
-        <v>16</v>
-      </c>
-      <c r="C123" t="n">
-        <v>-0.315593208511372</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" t="s">
-        <v>16</v>
-      </c>
-      <c r="C124" t="n">
-        <v>-0.429473014583396</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" t="s">
-        <v>16</v>
-      </c>
-      <c r="C125" t="n">
-        <v>0.612107075237315</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B126" t="s">
-        <v>16</v>
-      </c>
-      <c r="C126" t="n">
-        <v>-1.19509469158087</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" t="s">
-        <v>16</v>
-      </c>
-      <c r="C127" t="n">
-        <v>-1.0169864529567</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>15</v>
-      </c>
-      <c r="B128" t="s">
-        <v>16</v>
-      </c>
-      <c r="C128" t="n">
-        <v>-0.796743621321543</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" t="s">
-        <v>16</v>
-      </c>
-      <c r="C129" t="n">
-        <v>-1.04171733035753</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" t="s">
-        <v>16</v>
-      </c>
-      <c r="C130" t="n">
-        <v>-1.0819375547893</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" t="s">
-        <v>16</v>
-      </c>
-      <c r="C131" t="n">
-        <v>-2.03903034667916</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" t="s">
-        <v>16</v>
-      </c>
-      <c r="C132" t="n">
-        <v>-0.910903801319813</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" t="s">
-        <v>16</v>
-      </c>
-      <c r="C133" t="n">
-        <v>-0.78056974455948</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" t="s">
-        <v>16</v>
-      </c>
-      <c r="C134" t="n">
-        <v>-0.490659127276451</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" t="s">
-        <v>16</v>
-      </c>
-      <c r="C135" t="n">
-        <v>-0.356374828185775</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="s">
-        <v>16</v>
-      </c>
-      <c r="C136" t="n">
-        <v>-0.893631200026</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" t="n">
-        <v>-2.08541663383741</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="s">
-        <v>16</v>
-      </c>
-      <c r="C138" t="n">
-        <v>-1.47920385044012</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139" t="n">
-        <v>-1.594492232608</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" t="n">
-        <v>-0.536381800169944</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" t="n">
-        <v>-0.643718124689192</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" t="n">
-        <v>-0.677352931511474</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" t="n">
-        <v>-0.305262935318</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="n">
-        <v>-1.97117590608412</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" t="n">
-        <v>-0.0984363614637824</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" t="n">
-        <v>-0.195840709246273</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="s">
-        <v>16</v>
-      </c>
-      <c r="C147" t="n">
-        <v>-1.03664340939817</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" t="n">
-        <v>-1.94084639102376</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" t="n">
-        <v>-0.409096102587867</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" t="n">
-        <v>-0.206712187804619</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" t="n">
-        <v>-0.429566750022591</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="s">
-        <v>16</v>
-      </c>
-      <c r="C152" t="n">
-        <v>-0.707130760708442</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="s">
-        <v>16</v>
-      </c>
-      <c r="C153" t="n">
-        <v>-0.912476947560606</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" t="n">
-        <v>-0.614735692607501</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="s">
-        <v>16</v>
-      </c>
-      <c r="C155" t="n">
-        <v>-0.225350638057842</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" t="n">
-        <v>-0.674676897674754</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="s">
-        <v>16</v>
-      </c>
-      <c r="C157" t="n">
-        <v>-1.72959923313134</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="s">
-        <v>16</v>
-      </c>
-      <c r="C158" t="n">
-        <v>-1.32264934031798</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" t="n">
-        <v>-1.2432501021419</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="s">
-        <v>16</v>
-      </c>
-      <c r="C160" t="n">
-        <v>-0.290598374594986</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" t="n">
-        <v>-2.16141926101525</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>15</v>
-      </c>
-      <c r="B162" t="s">
-        <v>16</v>
-      </c>
-      <c r="C162" t="n">
-        <v>-0.995012113449608</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>15</v>
-      </c>
-      <c r="B163" t="s">
-        <v>16</v>
-      </c>
-      <c r="C163" t="n">
-        <v>-2.29196439684351</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" t="s">
-        <v>16</v>
-      </c>
-      <c r="C164" t="n">
-        <v>-0.398624306560128</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" t="s">
-        <v>16</v>
-      </c>
-      <c r="C165" t="n">
-        <v>-0.100528229957369</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>15</v>
-      </c>
-      <c r="B166" t="s">
-        <v>16</v>
-      </c>
-      <c r="C166" t="n">
-        <v>0.262151443101689</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>15</v>
-      </c>
-      <c r="B167" t="s">
-        <v>16</v>
-      </c>
-      <c r="C167" t="n">
-        <v>-0.701983158622824</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>15</v>
-      </c>
-      <c r="B168" t="s">
-        <v>16</v>
-      </c>
-      <c r="C168" t="n">
-        <v>-0.107213591884923</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>15</v>
-      </c>
-      <c r="B169" t="s">
-        <v>16</v>
-      </c>
-      <c r="C169" t="n">
-        <v>-0.818864140311881</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170" t="s">
-        <v>16</v>
-      </c>
-      <c r="C170" t="n">
-        <v>-1.46626399312771</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" t="s">
-        <v>16</v>
-      </c>
-      <c r="C171" t="n">
-        <v>-1.31300214919173</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" t="s">
-        <v>16</v>
-      </c>
-      <c r="C172" t="n">
-        <v>-2.1461369882344</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" t="s">
-        <v>16</v>
-      </c>
-      <c r="C173" t="n">
-        <v>-0.926775205299864</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>15</v>
-      </c>
-      <c r="B174" t="s">
-        <v>16</v>
-      </c>
-      <c r="C174" t="n">
-        <v>-1.26172941389989</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" t="n">
-        <v>-0.479673669644109</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="s">
-        <v>16</v>
-      </c>
-      <c r="C176" t="n">
-        <v>-0.775096474895438</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" t="n">
-        <v>-0.150012688317853</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="s">
-        <v>16</v>
-      </c>
-      <c r="C178" t="n">
-        <v>-0.751560184889121</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>15</v>
-      </c>
-      <c r="B179" t="s">
-        <v>16</v>
-      </c>
-      <c r="C179" t="n">
-        <v>-0.872005821025306</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>15</v>
-      </c>
-      <c r="B180" t="s">
-        <v>16</v>
-      </c>
-      <c r="C180" t="n">
-        <v>0.0574365706819083</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>15</v>
-      </c>
-      <c r="B181" t="s">
-        <v>16</v>
-      </c>
-      <c r="C181" t="n">
-        <v>-0.17866270988013</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>15</v>
-      </c>
-      <c r="B182" t="s">
-        <v>16</v>
-      </c>
-      <c r="C182" t="n">
-        <v>0.469002065572369</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>15</v>
-      </c>
-      <c r="B183" t="s">
-        <v>16</v>
-      </c>
-      <c r="C183" t="n">
-        <v>-2.14237986721272</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" t="s">
-        <v>16</v>
-      </c>
-      <c r="C184" t="n">
-        <v>-2.60128167484356</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>15</v>
-      </c>
-      <c r="B185" t="s">
-        <v>16</v>
-      </c>
-      <c r="C185" t="n">
-        <v>-0.833585961762394</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>15</v>
-      </c>
-      <c r="B186" t="s">
-        <v>16</v>
-      </c>
-      <c r="C186" t="n">
-        <v>-0.0425010681937719</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>15</v>
-      </c>
-      <c r="B187" t="s">
-        <v>16</v>
-      </c>
-      <c r="C187" t="n">
-        <v>-1.45141117263367</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>15</v>
-      </c>
-      <c r="B188" t="s">
-        <v>16</v>
-      </c>
-      <c r="C188" t="n">
-        <v>-0.169420512882721</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>15</v>
-      </c>
-      <c r="B189" t="s">
-        <v>16</v>
-      </c>
-      <c r="C189" t="n">
-        <v>-0.420280414796177</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>15</v>
-      </c>
-      <c r="B190" t="s">
-        <v>16</v>
-      </c>
-      <c r="C190" t="n">
-        <v>0.600651489835542</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>15</v>
-      </c>
-      <c r="B191" t="s">
-        <v>16</v>
-      </c>
-      <c r="C191" t="n">
-        <v>0.450978342074207</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>15</v>
-      </c>
-      <c r="B192" t="s">
-        <v>16</v>
-      </c>
-      <c r="C192" t="n">
-        <v>-2.06456842196727</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>15</v>
-      </c>
-      <c r="B193" t="s">
-        <v>16</v>
-      </c>
-      <c r="C193" t="n">
-        <v>-0.557354927744864</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>15</v>
-      </c>
-      <c r="B194" t="s">
-        <v>16</v>
-      </c>
-      <c r="C194" t="n">
-        <v>0.206339169505686</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>15</v>
-      </c>
-      <c r="B195" t="s">
-        <v>16</v>
-      </c>
-      <c r="C195" t="n">
-        <v>-0.781981664633485</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" t="s">
-        <v>16</v>
-      </c>
-      <c r="C196" t="n">
-        <v>-1.00086509241053</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>15</v>
-      </c>
-      <c r="B197" t="s">
-        <v>16</v>
-      </c>
-      <c r="C197" t="n">
-        <v>-1.01994162229937</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>15</v>
-      </c>
-      <c r="B198" t="s">
-        <v>16</v>
-      </c>
-      <c r="C198" t="n">
-        <v>-0.659082613265751</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>15</v>
-      </c>
-      <c r="B199" t="s">
-        <v>16</v>
-      </c>
-      <c r="C199" t="n">
-        <v>-2.99837245596622</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>15</v>
-      </c>
-      <c r="B200" t="s">
-        <v>16</v>
-      </c>
-      <c r="C200" t="n">
-        <v>-0.294323237866011</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>15</v>
-      </c>
-      <c r="B201" t="s">
-        <v>16</v>
-      </c>
-      <c r="C201" t="n">
-        <v>-1.18586536278553</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3361,7 +1159,7 @@
         <v>9.43</v>
       </c>
       <c r="E2" t="n">
-        <v>1.55677183762519</v>
+        <v>1.32558093230599</v>
       </c>
     </row>
     <row r="3">
@@ -3378,7 +1176,7 @@
         <v>20.73</v>
       </c>
       <c r="E3" t="n">
-        <v>4.79185945108245</v>
+        <v>4.78545435270518</v>
       </c>
     </row>
     <row r="4">
@@ -3395,7 +1193,7 @@
         <v>13.69</v>
       </c>
       <c r="E4" t="n">
-        <v>0.642945945776447</v>
+        <v>1.35645593408423</v>
       </c>
     </row>
     <row r="5">
@@ -3412,7 +1210,7 @@
         <v>10.45</v>
       </c>
       <c r="E5" t="n">
-        <v>-20.4383489163282</v>
+        <v>-20.3736736313515</v>
       </c>
     </row>
     <row r="6">
@@ -3429,7 +1227,7 @@
         <v>14.93</v>
       </c>
       <c r="E6" t="n">
-        <v>11.862137370573</v>
+        <v>11.2948375291683</v>
       </c>
     </row>
     <row r="7">
@@ -3446,7 +1244,7 @@
         <v>13.79</v>
       </c>
       <c r="E7" t="n">
-        <v>-5.43105426491957</v>
+        <v>-5.63780310678614</v>
       </c>
     </row>
     <row r="8">
@@ -3463,7 +1261,7 @@
         <v>0.79</v>
       </c>
       <c r="E8" t="n">
-        <v>4.33521366732614</v>
+        <v>4.24614937523447</v>
       </c>
     </row>
     <row r="9">
@@ -3480,7 +1278,7 @@
         <v>0.85</v>
       </c>
       <c r="E9" t="n">
-        <v>5.74152309479762</v>
+        <v>6.1064227683634</v>
       </c>
     </row>
     <row r="10">
@@ -3497,7 +1295,7 @@
         <v>-4.09</v>
       </c>
       <c r="E10" t="n">
-        <v>7.05406546810434</v>
+        <v>7.30579205439858</v>
       </c>
     </row>
     <row r="11">
@@ -3514,7 +1312,7 @@
         <v>-0.74</v>
       </c>
       <c r="E11" t="n">
-        <v>1.04713736157734</v>
+        <v>1.25996926897511</v>
       </c>
     </row>
     <row r="12">
@@ -3531,7 +1329,7 @@
         <v>-1.86</v>
       </c>
       <c r="E12" t="n">
-        <v>14.9960850380566</v>
+        <v>14.854888465038</v>
       </c>
     </row>
     <row r="13">
@@ -3548,7 +1346,7 @@
         <v>-6.6</v>
       </c>
       <c r="E13" t="n">
-        <v>3.67671633038585</v>
+        <v>3.18358993498523</v>
       </c>
     </row>
     <row r="14">
@@ -3565,7 +1363,7 @@
         <v>-5.99</v>
       </c>
       <c r="E14" t="n">
-        <v>4.58922942897388</v>
+        <v>4.95563160432245</v>
       </c>
     </row>
     <row r="15">
@@ -3582,7 +1380,7 @@
         <v>-0.48</v>
       </c>
       <c r="E15" t="n">
-        <v>1.56320177762326</v>
+        <v>2.23362745935307</v>
       </c>
     </row>
   </sheetData>
@@ -3692,10 +1490,10 @@
         <v>41</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>0.928571428571429</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="7">
@@ -3709,10 +1507,10 @@
         <v>42</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>0.928571428571429</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="8">
@@ -3896,10 +1694,10 @@
         <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>0.785714285714286</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="19">
@@ -3913,10 +1711,10 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
-        <v>0.785714285714286</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="20">
@@ -3964,10 +1762,10 @@
         <v>57</v>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E22" t="n">
-        <v>0.642857142857143</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="23">
@@ -3998,10 +1796,10 @@
         <v>59</v>
       </c>
       <c r="D24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>0.642857142857143</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="25">
@@ -4083,10 +1881,10 @@
         <v>64</v>
       </c>
       <c r="D29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="30">
@@ -4253,10 +2051,10 @@
         <v>74</v>
       </c>
       <c r="D39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>0.357142857142857</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="40">
@@ -4270,10 +2068,10 @@
         <v>75</v>
       </c>
       <c r="D40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E40" t="n">
-        <v>0.357142857142857</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="41">
@@ -4389,10 +2187,10 @@
         <v>82</v>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
-        <v>0.285714285714286</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="48">
@@ -6602,6 +4400,40 @@
         <v>1</v>
       </c>
       <c r="E177" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="s">
+        <v>213</v>
+      </c>
+      <c r="D178" t="n">
+        <v>1</v>
+      </c>
+      <c r="E178" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" t="s">
+        <v>214</v>
+      </c>
+      <c r="D179" t="n">
+        <v>1</v>
+      </c>
+      <c r="E179" t="n">
         <v>0.0714285714285714</v>
       </c>
     </row>

--- a/05_Figures/F06_prediction/proteins/total/comp_hypertrophy/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/total/comp_hypertrophy/spls/c_data/results.xlsx
@@ -1082,7 +1082,7 @@
         <v>1900</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>-1.41779861223299</v>
@@ -1090,10 +1090,18 @@
       <c r="I3" t="n">
         <v>-0.235164835164835</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="J3" t="n">
+        <v>0.81592039800995</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.517412935323383</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.798040345038692</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.77408265309442</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1117,6 +1125,2206 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-1.61562585162221</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-3.22465528386657</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.439169934377266</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-1.27717612200547</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-1.5591299818482</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.436329514483242</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-2.01966700631909</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.918778459267224</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-2.26831900975158</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.478380656863939</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-2.23380332505845</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-1.1446986446172</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.725461387918096</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.56794610029897</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-1.76696006725981</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-1.15521997861737</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.327998133009999</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.702029029589708</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-2.09093777375838</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-2.68967205182079</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.300675085853676</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-1.20212568437208</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-2.04497072516206</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-1.43985247151972</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.281969054699575</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-1.17120407849871</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-1.0839622403458</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.0281443303244756</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.345157693088436</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.032146580312677</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.779298856033742</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-1.32564652495337</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.589019192157078</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-0.319750315584714</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.885126366322508</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-1.38132017575407</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.95312842343724</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.0594000146895486</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-2.03914157009316</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-1.90541000690879</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-0.941391879839229</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-1.84021121994999</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-0.302129094640693</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-0.112822582391178</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-1.10335732974151</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-1.31032670360823</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-0.828935880084819</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-1.03901378981051</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-0.757208273818289</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.675758908488464</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-0.684669100094053</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-0.0631503927179411</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.425841273493399</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-0.439775700031331</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-0.832216084400047</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-0.683101610220713</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-0.312266717494801</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-1.29660946158441</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-2.09066779185685</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-0.527504368215791</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-1.17874607667674</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-0.993396852111144</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-0.9041781071715</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-0.596308479255837</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-0.433167410587222</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-1.41176990956985</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0.129315542943062</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.129673442194761</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-0.82537613393153</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0.00837782810208176</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-0.389258964968181</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-0.498883877323299</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-1.8680868207252</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-0.605709502774816</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0.217783494766843</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>-0.185160099447169</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-0.110974208670567</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-0.662135064547328</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-0.379238620394653</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-1.09003933192458</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-0.829203807664473</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-0.698392458591364</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-1.81593536519855</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-0.477659745604037</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0.0540299967200277</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="n">
+        <v>-0.31083243224704</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-0.113531750440121</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>-0.268807057472814</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="n">
+        <v>-0.659580789502268</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="n">
+        <v>-2.60825628710631</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="n">
+        <v>-2.22247107251221</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-0.916558451779211</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" t="n">
+        <v>-0.530376617660361</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="n">
+        <v>-0.979436243267375</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0.0256821951626703</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0.23647076063493</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="n">
+        <v>-1.43036847355339</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0.438812574873086</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0.209769948989891</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-0.753253946371489</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-0.289336201350894</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0.225637989346919</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-0.417819479974063</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0.449391311104598</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-0.610569874888952</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-1.62925993386654</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-0.100931038413735</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>0.345010132678497</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0.169383893741452</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-2.28636044606521</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-0.630152363110677</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-0.502176042154627</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="n">
+        <v>-1.18158467064211</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="n">
+        <v>0.102259525996975</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-0.552081310740882</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.0615390513228387</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-0.0532923597812645</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-0.602675313085375</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-0.403563497818655</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-0.805945345850964</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-2.37259151887618</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-0.345939848511327</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-0.421492794880844</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.551720077780407</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-1.16715365206946</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-1.23454786684243</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-0.852926149075981</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-0.985724352058766</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-1.02389062587027</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-2.28938749429805</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-1.04664276730841</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-0.791740395789855</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-0.670578168816876</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-0.309643257887702</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-1.07758411831192</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-2.18505615517196</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-1.38769667589981</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-1.73813985835965</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="n">
+        <v>-0.612398157080152</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-0.789688794073462</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-0.613749940077072</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.130645479616879</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="n">
+        <v>-1.10045478721304</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-0.0902209767845197</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="n">
+        <v>-0.0809916217037394</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-0.74348018478322</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-2.00406834915341</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="n">
+        <v>0.116097132777641</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-0.265480929198427</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="n">
+        <v>-0.338299761464524</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-0.575431206485559</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-0.878229944905753</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-0.567874485279896</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-0.268425928414976</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-0.677213159144176</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-1.57008092842435</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-1.2108627647843</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-1.20431569754494</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-0.248397569733533</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-2.03338213474236</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="n">
+        <v>-0.398794228951326</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-1.53966446499119</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-0.468432926099107</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-0.0613948943176172</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="n">
+        <v>0.210696229001586</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-0.519679736238917</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-0.0398631382911989</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-1.00531054567081</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-1.56876315753213</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-1.2719222090454</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-2.24910864487803</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-0.809018923409743</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="n">
+        <v>-1.10482281155679</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-0.4932044524546</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" t="n">
+        <v>-0.687048532649054</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-0.237819241266593</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="n">
+        <v>-0.603283829233098</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-0.44415571445216</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180" t="n">
+        <v>0.060153052270808</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="n">
+        <v>-0.601605997032008</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="n">
+        <v>0.382964721367241</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-2.02910802850235</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>-3.32405615597398</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" t="n">
+        <v>-1.08600838216431</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="n">
+        <v>0.175850071872271</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-1.13539583853721</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-0.206949634146983</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189" t="n">
+        <v>-0.421150942171777</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>0.66207260411469</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="n">
+        <v>0.61576194001847</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-2.77949968490581</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-0.453734717655266</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>16</v>
+      </c>
+      <c r="C194" t="n">
+        <v>0.316160207461987</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" t="n">
+        <v>-0.648121869942359</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>16</v>
+      </c>
+      <c r="C196" t="n">
+        <v>-0.873510543927361</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="s">
+        <v>16</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-1.67575757970702</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="s">
+        <v>16</v>
+      </c>
+      <c r="C198" t="n">
+        <v>-0.496501623766092</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-2.47840944833678</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-0.239923209836455</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-1.18152408469786</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
